--- a/public/tally_templates/PCSZ.xlsx
+++ b/public/tally_templates/PCSZ.xlsx
@@ -1061,7 +1061,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:ns4="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac x16r2">
   <numFmts count="9">
     <numFmt numFmtId="164" formatCode="_ * #,##0_ ;_ * -#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* (#,##0);_(* &quot;-&quot;_);_(@_)"/>
@@ -2945,7 +2945,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="619">
+  <cellXfs count="657">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -4776,6 +4776,120 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="94" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="94" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="76" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="94" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="106" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="108" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4784,11 +4898,11 @@
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <ns3:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <ns4:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -5056,7 +5170,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -5868,7 +5982,7 @@
       <c r="G8" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="H8" s="14" t="s">
+      <c r="H8" s="620" t="s">
         <v>105</v>
       </c>
       <c r="I8" s="14"/>
@@ -7064,7 +7178,7 @@
       <c r="G50" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="H50" s="14" t="s">
+      <c r="H50" s="620" t="s">
         <v>105</v>
       </c>
       <c r="I50" s="14"/>
@@ -7189,27 +7303,17 @@
       <c r="Y53" s="5"/>
     </row>
     <row r="54" ht="20.1" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A54" s="406" t="s">
-        <v>115</v>
-      </c>
+      <c r="A54" s="406"/>
       <c r="B54" s="435"/>
-      <c r="C54" s="435" t="s">
-        <v>116</v>
-      </c>
+      <c r="C54" s="435"/>
       <c r="D54" s="436"/>
       <c r="E54" s="437"/>
-      <c r="F54" s="410">
-        <v>-40</v>
-      </c>
-      <c r="G54" s="410">
-        <v>-38.7</v>
-      </c>
+      <c r="F54" s="410"/>
+      <c r="G54" s="410"/>
       <c r="H54" s="411" t="s">
         <v>117</v>
       </c>
-      <c r="I54" s="435" t="s">
-        <v>118</v>
-      </c>
+      <c r="I54" s="435"/>
       <c r="J54" s="5"/>
       <c r="K54" s="5"/>
       <c r="L54" s="5"/>
@@ -7228,27 +7332,15 @@
       <c r="Y54" s="5"/>
     </row>
     <row r="55" ht="20.1" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A55" s="417" t="s">
-        <v>119</v>
-      </c>
+      <c r="A55" s="417"/>
       <c r="B55" s="438"/>
-      <c r="C55" s="438" t="s">
-        <v>116</v>
-      </c>
+      <c r="C55" s="438"/>
       <c r="D55" s="439"/>
       <c r="E55" s="440"/>
-      <c r="F55" s="415">
-        <v>-40</v>
-      </c>
-      <c r="G55" s="415">
-        <v>-36</v>
-      </c>
-      <c r="H55" s="441" t="s">
-        <v>120</v>
-      </c>
-      <c r="I55" s="438" t="s">
-        <v>118</v>
-      </c>
+      <c r="F55" s="415"/>
+      <c r="G55" s="415"/>
+      <c r="H55" s="441"/>
+      <c r="I55" s="438"/>
       <c r="J55" s="5"/>
       <c r="K55" s="5"/>
       <c r="L55" s="5"/>
@@ -8268,7 +8360,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor indexed="59"/>
     <pageSetUpPr fitToPage="1"/>
@@ -9069,7 +9161,7 @@
       <c r="A8" s="194" t="s">
         <v>61</v>
       </c>
-      <c r="B8" s="194" t="s">
+      <c r="B8" s="156" t="s">
         <v>25</v>
       </c>
       <c r="C8" s="194"/>
@@ -9081,7 +9173,7 @@
         <v>62</v>
       </c>
       <c r="I8" s="179"/>
-      <c r="J8" s="179" t="s">
+      <c r="J8" s="156" t="s">
         <v>63</v>
       </c>
       <c r="K8" s="179"/>
@@ -9132,7 +9224,7 @@
       <c r="X9" s="140"/>
       <c r="Y9" s="140"/>
     </row>
-    <row r="10" ht="12" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="199" t="s">
         <v>11</v>
       </c>
@@ -9173,7 +9265,7 @@
       <c r="X10" s="140"/>
       <c r="Y10" s="140"/>
     </row>
-    <row r="11" ht="12" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="203"/>
       <c r="B11" s="203"/>
       <c r="C11" s="261"/>
@@ -9989,7 +10081,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor indexed="59"/>
   </sheetPr>
@@ -10345,7 +10437,7 @@
       <c r="A4" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="619" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="5"/>
@@ -10354,14 +10446,14 @@
       <c r="F4" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="14"/>
+      <c r="G4" s="620"/>
       <c r="H4" s="14"/>
       <c r="I4" s="14"/>
       <c r="J4" s="5"/>
       <c r="K4" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="L4" s="15"/>
+      <c r="L4" s="621"/>
       <c r="M4" s="14"/>
       <c r="N4" s="14"/>
       <c r="O4" s="14"/>
@@ -10407,21 +10499,21 @@
       <c r="A6" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="17"/>
+      <c r="B6" s="622"/>
       <c r="C6" s="5"/>
       <c r="D6" s="9"/>
       <c r="E6" s="18"/>
       <c r="F6" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="14"/>
+      <c r="G6" s="620"/>
       <c r="H6" s="14"/>
       <c r="I6" s="14"/>
       <c r="J6" s="5"/>
       <c r="K6" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="L6" s="19" t="s">
+      <c r="L6" s="623" t="s">
         <v>9</v>
       </c>
       <c r="M6" s="19"/>
@@ -12930,7 +13022,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="1" tint="0.499984740745262"/>
   </sheetPr>
@@ -13614,7 +13706,7 @@
       <c r="O6" s="258" t="s">
         <v>4</v>
       </c>
-      <c r="P6" s="139"/>
+      <c r="P6" s="655"/>
       <c r="Q6" s="139"/>
       <c r="R6" s="119" t="str">
         <f>'Final Work'!G4</f>
@@ -13686,7 +13778,7 @@
       <c r="A8" s="463" t="s">
         <v>130</v>
       </c>
-      <c r="B8" s="463"/>
+      <c r="B8" s="656"/>
       <c r="C8" s="463"/>
       <c r="D8" s="464" t="s">
         <v>63</v>
@@ -13704,7 +13796,7 @@
       <c r="O8" s="464" t="s">
         <v>7</v>
       </c>
-      <c r="P8" s="463"/>
+      <c r="P8" s="656"/>
       <c r="Q8" s="463"/>
       <c r="R8" s="462">
         <f>'Final Work'!G6</f>
@@ -13721,7 +13813,7 @@
       </c>
       <c r="Z8" s="462"/>
       <c r="AA8" s="462"/>
-      <c r="AB8" s="462" t="s">
+      <c r="AB8" s="656" t="s">
         <v>25</v>
       </c>
       <c r="AC8" s="462"/>
@@ -17901,7 +17993,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor indexed="60"/>
     <pageSetUpPr fitToPage="1"/>
@@ -18708,13 +18800,13 @@
       <c r="G6" s="140" t="s">
         <v>38</v>
       </c>
-      <c r="H6" s="179"/>
+      <c r="H6" s="156"/>
       <c r="I6" s="179"/>
       <c r="J6" s="140"/>
       <c r="K6" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="L6" s="195"/>
+      <c r="L6" s="633"/>
       <c r="M6" s="179"/>
       <c r="N6" s="5"/>
       <c r="O6" s="140"/>
@@ -18760,7 +18852,7 @@
       <c r="A8" s="194" t="s">
         <v>40</v>
       </c>
-      <c r="B8" s="140" t="s">
+      <c r="B8" s="634" t="s">
         <v>25</v>
       </c>
       <c r="C8" s="140"/>
@@ -18770,13 +18862,13 @@
       <c r="G8" s="140" t="s">
         <v>41</v>
       </c>
-      <c r="H8" s="179"/>
+      <c r="H8" s="156"/>
       <c r="I8" s="179"/>
       <c r="J8" s="140"/>
       <c r="K8" s="194" t="s">
         <v>42</v>
       </c>
-      <c r="L8" s="179"/>
+      <c r="L8" s="156"/>
       <c r="M8" s="179"/>
       <c r="N8" s="140"/>
       <c r="O8" s="140"/>
@@ -18818,7 +18910,7 @@
       <c r="X9" s="140"/>
       <c r="Y9" s="140"/>
     </row>
-    <row r="10" ht="14.4" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="196" t="s">
         <v>43</v>
       </c>
@@ -18863,7 +18955,7 @@
       <c r="X10" s="140"/>
       <c r="Y10" s="140"/>
     </row>
-    <row r="11" ht="14.4" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="200"/>
       <c r="B11" s="201"/>
       <c r="C11" s="202"/>
@@ -18897,15 +18989,15 @@
       <c r="B12" s="205"/>
       <c r="C12" s="206"/>
       <c r="D12" s="205"/>
-      <c r="E12" s="207"/>
-      <c r="F12" s="208"/>
+      <c r="E12" s="635"/>
+      <c r="F12" s="206"/>
       <c r="G12" s="204"/>
       <c r="H12" s="209"/>
       <c r="I12" s="210"/>
       <c r="J12" s="211"/>
       <c r="K12" s="204"/>
       <c r="L12" s="204"/>
-      <c r="M12" s="212"/>
+      <c r="M12" s="636"/>
       <c r="N12" s="140"/>
       <c r="O12" s="140"/>
       <c r="P12" s="140"/>
@@ -18924,15 +19016,15 @@
       <c r="B13" s="214"/>
       <c r="C13" s="215"/>
       <c r="D13" s="214"/>
-      <c r="E13" s="216"/>
-      <c r="F13" s="217"/>
+      <c r="E13" s="637"/>
+      <c r="F13" s="215"/>
       <c r="G13" s="213"/>
       <c r="H13" s="218"/>
       <c r="I13" s="219"/>
       <c r="J13" s="218"/>
       <c r="K13" s="213"/>
       <c r="L13" s="213"/>
-      <c r="M13" s="220"/>
+      <c r="M13" s="638"/>
       <c r="N13" s="140"/>
       <c r="O13" s="140"/>
       <c r="P13" s="140"/>
@@ -18951,15 +19043,15 @@
       <c r="B14" s="222"/>
       <c r="C14" s="223"/>
       <c r="D14" s="222"/>
-      <c r="E14" s="224"/>
-      <c r="F14" s="225"/>
+      <c r="E14" s="639"/>
+      <c r="F14" s="223"/>
       <c r="G14" s="221"/>
       <c r="H14" s="226"/>
       <c r="I14" s="227"/>
       <c r="J14" s="228"/>
       <c r="K14" s="221"/>
       <c r="L14" s="221"/>
-      <c r="M14" s="229"/>
+      <c r="M14" s="640"/>
       <c r="N14" s="140"/>
       <c r="O14" s="140"/>
       <c r="P14" s="140"/>
@@ -18978,15 +19070,15 @@
       <c r="B15" s="214"/>
       <c r="C15" s="215"/>
       <c r="D15" s="214"/>
-      <c r="E15" s="216"/>
-      <c r="F15" s="217"/>
+      <c r="E15" s="637"/>
+      <c r="F15" s="215"/>
       <c r="G15" s="213"/>
       <c r="H15" s="218"/>
       <c r="I15" s="219"/>
       <c r="J15" s="218"/>
       <c r="K15" s="213"/>
       <c r="L15" s="213"/>
-      <c r="M15" s="220"/>
+      <c r="M15" s="638"/>
       <c r="N15" s="140"/>
       <c r="O15" s="140"/>
       <c r="P15" s="140"/>
@@ -19001,19 +19093,19 @@
       <c r="Y15" s="140"/>
     </row>
     <row r="16" ht="27" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A16" s="230"/>
+      <c r="A16" s="641"/>
       <c r="B16" s="222"/>
       <c r="C16" s="223"/>
       <c r="D16" s="222"/>
-      <c r="E16" s="224"/>
-      <c r="F16" s="225"/>
+      <c r="E16" s="639"/>
+      <c r="F16" s="223"/>
       <c r="G16" s="221"/>
       <c r="H16" s="226"/>
       <c r="I16" s="227"/>
       <c r="J16" s="228"/>
       <c r="K16" s="221"/>
       <c r="L16" s="221"/>
-      <c r="M16" s="231"/>
+      <c r="M16" s="642"/>
       <c r="N16" s="140"/>
       <c r="O16" s="140"/>
       <c r="P16" s="140"/>
@@ -19746,7 +19838,7 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor indexed="60"/>
     <pageSetUpPr fitToPage="1"/>
@@ -20547,7 +20639,7 @@
       <c r="A8" s="194" t="s">
         <v>61</v>
       </c>
-      <c r="B8" s="194" t="s">
+      <c r="B8" s="156" t="s">
         <v>25</v>
       </c>
       <c r="C8" s="194"/>
@@ -20559,7 +20651,7 @@
         <v>62</v>
       </c>
       <c r="I8" s="179"/>
-      <c r="J8" s="179" t="s">
+      <c r="J8" s="156" t="s">
         <v>63</v>
       </c>
       <c r="K8" s="179"/>
@@ -20610,7 +20702,7 @@
       <c r="X9" s="140"/>
       <c r="Y9" s="140"/>
     </row>
-    <row r="10" ht="12" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="196" t="s">
         <v>11</v>
       </c>
@@ -20651,7 +20743,7 @@
       <c r="X10" s="140"/>
       <c r="Y10" s="140"/>
     </row>
-    <row r="11" ht="12" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="200"/>
       <c r="B11" s="200"/>
       <c r="C11" s="261"/>
@@ -21467,7 +21559,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -22134,17 +22226,17 @@
       <c r="A6" s="144" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="145"/>
+      <c r="B6" s="624"/>
       <c r="C6" s="144" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="14"/>
+      <c r="D6" s="620"/>
       <c r="E6" s="14"/>
       <c r="F6" s="11"/>
       <c r="G6" s="146" t="s">
         <v>5</v>
       </c>
-      <c r="H6" s="147"/>
+      <c r="H6" s="625"/>
       <c r="I6" s="11"/>
       <c r="J6" s="11"/>
       <c r="K6" s="11"/>
@@ -22194,17 +22286,17 @@
       <c r="A8" s="144" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="148"/>
+      <c r="B8" s="620"/>
       <c r="C8" s="144" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="14"/>
+      <c r="D8" s="620"/>
       <c r="E8" s="14"/>
       <c r="F8" s="144"/>
       <c r="G8" s="149" t="s">
         <v>30</v>
       </c>
-      <c r="H8" s="19"/>
+      <c r="H8" s="623"/>
       <c r="I8" s="11"/>
       <c r="J8" s="11"/>
       <c r="K8" s="11"/>
@@ -22342,7 +22434,7 @@
         <v>34</v>
       </c>
       <c r="B13" s="154"/>
-      <c r="C13" s="155"/>
+      <c r="C13" s="626"/>
       <c r="D13" s="155"/>
       <c r="E13" s="155"/>
       <c r="F13" s="155"/>
@@ -22369,7 +22461,7 @@
     <row r="14" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A14" s="157"/>
       <c r="B14" s="158"/>
-      <c r="C14" s="159"/>
+      <c r="C14" s="627"/>
       <c r="D14" s="159"/>
       <c r="E14" s="159"/>
       <c r="F14" s="159"/>
@@ -22396,7 +22488,7 @@
     <row r="15" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A15" s="157"/>
       <c r="B15" s="58"/>
-      <c r="C15" s="160"/>
+      <c r="C15" s="628"/>
       <c r="D15" s="161"/>
       <c r="E15" s="161"/>
       <c r="F15" s="161"/>
@@ -22423,7 +22515,7 @@
     <row r="16" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A16" s="157"/>
       <c r="B16" s="163"/>
-      <c r="C16" s="164"/>
+      <c r="C16" s="629"/>
       <c r="D16" s="165"/>
       <c r="E16" s="165"/>
       <c r="F16" s="165"/>
@@ -22450,7 +22542,7 @@
     <row r="17" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A17" s="167"/>
       <c r="B17" s="168"/>
-      <c r="C17" s="169"/>
+      <c r="C17" s="630"/>
       <c r="D17" s="170"/>
       <c r="E17" s="170"/>
       <c r="F17" s="170"/>
@@ -22477,7 +22569,7 @@
     <row r="18" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A18" s="31"/>
       <c r="B18" s="58"/>
-      <c r="C18" s="160"/>
+      <c r="C18" s="628"/>
       <c r="D18" s="161"/>
       <c r="E18" s="161"/>
       <c r="F18" s="161"/>
@@ -22504,7 +22596,7 @@
     <row r="19" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A19" s="172"/>
       <c r="B19" s="163"/>
-      <c r="C19" s="164"/>
+      <c r="C19" s="629"/>
       <c r="D19" s="165"/>
       <c r="E19" s="165"/>
       <c r="F19" s="165"/>
@@ -22531,7 +22623,7 @@
     <row r="20" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A20" s="157"/>
       <c r="B20" s="163"/>
-      <c r="C20" s="164"/>
+      <c r="C20" s="629"/>
       <c r="D20" s="165"/>
       <c r="E20" s="165"/>
       <c r="F20" s="165"/>
@@ -22558,7 +22650,7 @@
     <row r="21" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A21" s="173"/>
       <c r="B21" s="163"/>
-      <c r="C21" s="164"/>
+      <c r="C21" s="629"/>
       <c r="D21" s="165"/>
       <c r="E21" s="165"/>
       <c r="F21" s="165"/>
@@ -22585,7 +22677,7 @@
     <row r="22" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A22" s="174"/>
       <c r="B22" s="168"/>
-      <c r="C22" s="169"/>
+      <c r="C22" s="630"/>
       <c r="D22" s="170"/>
       <c r="E22" s="170"/>
       <c r="F22" s="170"/>
@@ -22612,7 +22704,7 @@
     <row r="23" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A23" s="175"/>
       <c r="B23" s="58"/>
-      <c r="C23" s="160"/>
+      <c r="C23" s="628"/>
       <c r="D23" s="161"/>
       <c r="E23" s="161"/>
       <c r="F23" s="161"/>
@@ -22639,7 +22731,7 @@
     <row r="24" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A24" s="176"/>
       <c r="B24" s="177"/>
-      <c r="C24" s="178"/>
+      <c r="C24" s="631"/>
       <c r="D24" s="178"/>
       <c r="E24" s="178"/>
       <c r="F24" s="178"/>
@@ -22666,7 +22758,7 @@
     <row r="25" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A25" s="167"/>
       <c r="B25" s="58"/>
-      <c r="C25" s="160"/>
+      <c r="C25" s="628"/>
       <c r="D25" s="161"/>
       <c r="E25" s="161"/>
       <c r="F25" s="161"/>
@@ -22693,7 +22785,7 @@
     <row r="26" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A26" s="157"/>
       <c r="B26" s="163"/>
-      <c r="C26" s="164"/>
+      <c r="C26" s="629"/>
       <c r="D26" s="165"/>
       <c r="E26" s="165"/>
       <c r="F26" s="165"/>
@@ -22720,7 +22812,7 @@
     <row r="27" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A27" s="180"/>
       <c r="B27" s="168"/>
-      <c r="C27" s="169"/>
+      <c r="C27" s="630"/>
       <c r="D27" s="170"/>
       <c r="E27" s="170"/>
       <c r="F27" s="170"/>
@@ -22747,7 +22839,7 @@
     <row r="28" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A28" s="31"/>
       <c r="B28" s="29"/>
-      <c r="C28" s="181"/>
+      <c r="C28" s="632"/>
       <c r="D28" s="182"/>
       <c r="E28" s="182"/>
       <c r="F28" s="182"/>
@@ -22774,7 +22866,7 @@
     <row r="29" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A29" s="157"/>
       <c r="B29" s="58"/>
-      <c r="C29" s="160"/>
+      <c r="C29" s="628"/>
       <c r="D29" s="161"/>
       <c r="E29" s="161"/>
       <c r="F29" s="161"/>
@@ -22801,7 +22893,7 @@
     <row r="30" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A30" s="157"/>
       <c r="B30" s="58"/>
-      <c r="C30" s="160"/>
+      <c r="C30" s="628"/>
       <c r="D30" s="161"/>
       <c r="E30" s="161"/>
       <c r="F30" s="161"/>
@@ -22828,7 +22920,7 @@
     <row r="31" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A31" s="157"/>
       <c r="B31" s="58"/>
-      <c r="C31" s="160"/>
+      <c r="C31" s="628"/>
       <c r="D31" s="161"/>
       <c r="E31" s="161"/>
       <c r="F31" s="161"/>
@@ -22855,7 +22947,7 @@
     <row r="32" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A32" s="167"/>
       <c r="B32" s="168"/>
-      <c r="C32" s="169"/>
+      <c r="C32" s="630"/>
       <c r="D32" s="170"/>
       <c r="E32" s="170"/>
       <c r="F32" s="170"/>
@@ -22882,7 +22974,7 @@
     <row r="33" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A33" s="31"/>
       <c r="B33" s="29"/>
-      <c r="C33" s="181"/>
+      <c r="C33" s="632"/>
       <c r="D33" s="182"/>
       <c r="E33" s="182"/>
       <c r="F33" s="182"/>
@@ -22911,7 +23003,7 @@
         <v>35</v>
       </c>
       <c r="B34" s="177"/>
-      <c r="C34" s="178"/>
+      <c r="C34" s="631"/>
       <c r="D34" s="178"/>
       <c r="E34" s="178"/>
       <c r="F34" s="178"/>
@@ -22938,7 +23030,7 @@
     <row r="35" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A35" s="184"/>
       <c r="B35" s="163"/>
-      <c r="C35" s="164"/>
+      <c r="C35" s="629"/>
       <c r="D35" s="165"/>
       <c r="E35" s="165"/>
       <c r="F35" s="165"/>
@@ -22965,7 +23057,7 @@
     <row r="36" ht="20.1" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A36" s="185"/>
       <c r="B36" s="163"/>
-      <c r="C36" s="164"/>
+      <c r="C36" s="629"/>
       <c r="D36" s="165"/>
       <c r="E36" s="165"/>
       <c r="F36" s="165"/>
@@ -22992,7 +23084,7 @@
     <row r="37" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A37" s="187"/>
       <c r="B37" s="168"/>
-      <c r="C37" s="169"/>
+      <c r="C37" s="630"/>
       <c r="D37" s="170"/>
       <c r="E37" s="170"/>
       <c r="F37" s="170"/>
@@ -23019,7 +23111,7 @@
     <row r="38" ht="20.1" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A38" s="188"/>
       <c r="B38" s="163"/>
-      <c r="C38" s="164"/>
+      <c r="C38" s="629"/>
       <c r="D38" s="165"/>
       <c r="E38" s="165"/>
       <c r="F38" s="165"/>
@@ -23046,7 +23138,7 @@
     <row r="39" ht="20.1" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A39" s="185"/>
       <c r="B39" s="163"/>
-      <c r="C39" s="164"/>
+      <c r="C39" s="629"/>
       <c r="D39" s="165"/>
       <c r="E39" s="165"/>
       <c r="F39" s="165"/>
@@ -23073,7 +23165,7 @@
     <row r="40" ht="20.1" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A40" s="185"/>
       <c r="B40" s="177"/>
-      <c r="C40" s="178"/>
+      <c r="C40" s="631"/>
       <c r="D40" s="178"/>
       <c r="E40" s="178"/>
       <c r="F40" s="178"/>
@@ -23100,7 +23192,7 @@
     <row r="41" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A41" s="157"/>
       <c r="B41" s="163"/>
-      <c r="C41" s="164"/>
+      <c r="C41" s="629"/>
       <c r="D41" s="165"/>
       <c r="E41" s="165"/>
       <c r="F41" s="165"/>
@@ -23127,7 +23219,7 @@
     <row r="42" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A42" s="157"/>
       <c r="B42" s="158"/>
-      <c r="C42" s="178"/>
+      <c r="C42" s="631"/>
       <c r="D42" s="178"/>
       <c r="E42" s="178"/>
       <c r="F42" s="178"/>
@@ -23397,7 +23489,7 @@
       <c r="Y51" s="140"/>
     </row>
   </sheetData>
-  <mergeCells count="39">
+  <mergeCells count="41">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="C3:F3"/>
@@ -23437,6 +23529,8 @@
     <mergeCell ref="C42:H42"/>
     <mergeCell ref="A46:B46"/>
     <mergeCell ref="G46:H46"/>
+    <mergeCell ref="C43:H43"/>
+    <mergeCell ref="C44:H44"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.3937007874015748" right="0.3937007874015748" top="0.3937007874015748" bottom="0.3937007874015748" header="0.5118110236220472" footer="0.35433070866141736"/>
@@ -23445,7 +23539,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor indexed="59"/>
     <pageSetUpPr fitToPage="1"/>
@@ -24250,13 +24344,13 @@
       <c r="G6" s="140" t="s">
         <v>38</v>
       </c>
-      <c r="H6" s="179"/>
+      <c r="H6" s="156"/>
       <c r="I6" s="179"/>
       <c r="J6" s="140"/>
       <c r="K6" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="L6" s="195"/>
+      <c r="L6" s="633"/>
       <c r="M6" s="179"/>
       <c r="N6" s="5"/>
       <c r="O6" s="140"/>
@@ -24302,7 +24396,7 @@
       <c r="A8" s="194" t="s">
         <v>72</v>
       </c>
-      <c r="B8" s="140" t="s">
+      <c r="B8" s="634" t="s">
         <v>25</v>
       </c>
       <c r="C8" s="273"/>
@@ -24312,13 +24406,13 @@
       <c r="G8" s="140" t="s">
         <v>41</v>
       </c>
-      <c r="H8" s="179"/>
+      <c r="H8" s="156"/>
       <c r="I8" s="179"/>
       <c r="J8" s="140"/>
       <c r="K8" s="194" t="s">
         <v>42</v>
       </c>
-      <c r="L8" s="179"/>
+      <c r="L8" s="156"/>
       <c r="M8" s="179"/>
       <c r="N8" s="140"/>
       <c r="O8" s="140"/>
@@ -24360,7 +24454,7 @@
       <c r="X9" s="140"/>
       <c r="Y9" s="140"/>
     </row>
-    <row r="10" ht="14.4" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="274" t="s">
         <v>43</v>
       </c>
@@ -24405,7 +24499,7 @@
       <c r="X10" s="140"/>
       <c r="Y10" s="140"/>
     </row>
-    <row r="11" ht="14.4" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="200"/>
       <c r="B11" s="201"/>
       <c r="C11" s="202"/>
@@ -24439,15 +24533,15 @@
       <c r="B12" s="204"/>
       <c r="C12" s="204"/>
       <c r="D12" s="205"/>
-      <c r="E12" s="275"/>
-      <c r="F12" s="276"/>
+      <c r="E12" s="643"/>
+      <c r="F12" s="644"/>
       <c r="G12" s="204"/>
       <c r="H12" s="211"/>
       <c r="I12" s="277"/>
       <c r="J12" s="278"/>
       <c r="K12" s="204"/>
       <c r="L12" s="204"/>
-      <c r="M12" s="279"/>
+      <c r="M12" s="645"/>
       <c r="N12" s="140"/>
       <c r="O12" s="140"/>
       <c r="P12" s="140"/>
@@ -24466,15 +24560,15 @@
       <c r="B13" s="213"/>
       <c r="C13" s="213"/>
       <c r="D13" s="222"/>
-      <c r="E13" s="280"/>
-      <c r="F13" s="281"/>
+      <c r="E13" s="646"/>
+      <c r="F13" s="647"/>
       <c r="G13" s="213"/>
       <c r="H13" s="282"/>
       <c r="I13" s="283"/>
       <c r="J13" s="218"/>
       <c r="K13" s="213"/>
       <c r="L13" s="213"/>
-      <c r="M13" s="229"/>
+      <c r="M13" s="640"/>
       <c r="N13" s="140"/>
       <c r="O13" s="140"/>
       <c r="P13" s="140"/>
@@ -24493,15 +24587,15 @@
       <c r="B14" s="213"/>
       <c r="C14" s="213"/>
       <c r="D14" s="214"/>
-      <c r="E14" s="280"/>
-      <c r="F14" s="281"/>
+      <c r="E14" s="646"/>
+      <c r="F14" s="647"/>
       <c r="G14" s="213"/>
       <c r="H14" s="282"/>
       <c r="I14" s="283"/>
       <c r="J14" s="218"/>
       <c r="K14" s="213"/>
       <c r="L14" s="213"/>
-      <c r="M14" s="220"/>
+      <c r="M14" s="638"/>
       <c r="N14" s="140"/>
       <c r="O14" s="140"/>
       <c r="P14" s="140"/>
@@ -24520,15 +24614,15 @@
       <c r="B15" s="213"/>
       <c r="C15" s="213"/>
       <c r="D15" s="214"/>
-      <c r="E15" s="280"/>
-      <c r="F15" s="281"/>
+      <c r="E15" s="646"/>
+      <c r="F15" s="647"/>
       <c r="G15" s="213"/>
       <c r="H15" s="282"/>
       <c r="I15" s="283"/>
       <c r="J15" s="218"/>
       <c r="K15" s="213"/>
       <c r="L15" s="213"/>
-      <c r="M15" s="220"/>
+      <c r="M15" s="638"/>
       <c r="N15" s="140"/>
       <c r="O15" s="140"/>
       <c r="P15" s="140"/>
@@ -24547,15 +24641,15 @@
       <c r="B16" s="213"/>
       <c r="C16" s="213"/>
       <c r="D16" s="214"/>
-      <c r="E16" s="280"/>
-      <c r="F16" s="281"/>
+      <c r="E16" s="646"/>
+      <c r="F16" s="647"/>
       <c r="G16" s="213"/>
       <c r="H16" s="282"/>
       <c r="I16" s="283"/>
       <c r="J16" s="218"/>
       <c r="K16" s="213"/>
       <c r="L16" s="213"/>
-      <c r="M16" s="220"/>
+      <c r="M16" s="638"/>
       <c r="N16" s="140"/>
       <c r="O16" s="140"/>
       <c r="P16" s="140"/>
@@ -24574,15 +24668,15 @@
       <c r="B17" s="214"/>
       <c r="C17" s="215"/>
       <c r="D17" s="214"/>
-      <c r="E17" s="280"/>
-      <c r="F17" s="281"/>
+      <c r="E17" s="646"/>
+      <c r="F17" s="647"/>
       <c r="G17" s="213"/>
       <c r="H17" s="282"/>
       <c r="I17" s="283"/>
       <c r="J17" s="218"/>
       <c r="K17" s="213"/>
       <c r="L17" s="213"/>
-      <c r="M17" s="220"/>
+      <c r="M17" s="638"/>
       <c r="N17" s="140"/>
       <c r="O17" s="140"/>
       <c r="P17" s="140"/>
@@ -24601,15 +24695,15 @@
       <c r="B18" s="213"/>
       <c r="C18" s="213"/>
       <c r="D18" s="214"/>
-      <c r="E18" s="280"/>
-      <c r="F18" s="281"/>
+      <c r="E18" s="646"/>
+      <c r="F18" s="647"/>
       <c r="G18" s="213"/>
       <c r="H18" s="282"/>
       <c r="I18" s="283"/>
       <c r="J18" s="218"/>
       <c r="K18" s="213"/>
       <c r="L18" s="213"/>
-      <c r="M18" s="220"/>
+      <c r="M18" s="638"/>
       <c r="N18" s="140"/>
       <c r="O18" s="140"/>
       <c r="P18" s="140"/>
@@ -24628,15 +24722,15 @@
       <c r="B19" s="213"/>
       <c r="C19" s="213"/>
       <c r="D19" s="214"/>
-      <c r="E19" s="280"/>
-      <c r="F19" s="281"/>
+      <c r="E19" s="646"/>
+      <c r="F19" s="647"/>
       <c r="G19" s="213"/>
       <c r="H19" s="282"/>
       <c r="I19" s="283"/>
       <c r="J19" s="218"/>
       <c r="K19" s="213"/>
       <c r="L19" s="213"/>
-      <c r="M19" s="220"/>
+      <c r="M19" s="638"/>
       <c r="N19" s="140"/>
       <c r="O19" s="140"/>
       <c r="P19" s="140"/>
@@ -24655,15 +24749,15 @@
       <c r="B20" s="213"/>
       <c r="C20" s="213"/>
       <c r="D20" s="214"/>
-      <c r="E20" s="280"/>
-      <c r="F20" s="281"/>
+      <c r="E20" s="646"/>
+      <c r="F20" s="647"/>
       <c r="G20" s="213"/>
       <c r="H20" s="282"/>
       <c r="I20" s="283"/>
       <c r="J20" s="218"/>
       <c r="K20" s="213"/>
       <c r="L20" s="213"/>
-      <c r="M20" s="220"/>
+      <c r="M20" s="638"/>
       <c r="N20" s="140"/>
       <c r="O20" s="140"/>
       <c r="P20" s="140"/>
@@ -24682,15 +24776,15 @@
       <c r="B21" s="221"/>
       <c r="C21" s="221"/>
       <c r="D21" s="222"/>
-      <c r="E21" s="284"/>
-      <c r="F21" s="285"/>
+      <c r="E21" s="648"/>
+      <c r="F21" s="649"/>
       <c r="G21" s="221"/>
       <c r="H21" s="228"/>
       <c r="I21" s="286"/>
       <c r="J21" s="218"/>
       <c r="K21" s="221"/>
       <c r="L21" s="221"/>
-      <c r="M21" s="229"/>
+      <c r="M21" s="640"/>
       <c r="N21" s="140"/>
       <c r="O21" s="140"/>
       <c r="P21" s="140"/>
@@ -25329,7 +25423,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -26012,7 +26106,7 @@
       <c r="F4" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="G4" s="195"/>
+      <c r="G4" s="633"/>
       <c r="H4" s="179"/>
       <c r="I4" s="140"/>
       <c r="J4" s="140"/>
@@ -26075,7 +26169,7 @@
       <c r="F6" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="G6" s="310" t="s">
+      <c r="G6" s="650" t="s">
         <v>25</v>
       </c>
       <c r="H6" s="140"/>
@@ -26718,12 +26812,12 @@
     <row r="29" ht="21.9" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A29" s="354"/>
       <c r="B29" s="355"/>
-      <c r="C29" s="356"/>
-      <c r="D29" s="356"/>
-      <c r="E29" s="356"/>
-      <c r="F29" s="356"/>
-      <c r="G29" s="356"/>
-      <c r="H29" s="357"/>
+      <c r="C29" s="651"/>
+      <c r="D29" s="651"/>
+      <c r="E29" s="651"/>
+      <c r="F29" s="651"/>
+      <c r="G29" s="651"/>
+      <c r="H29" s="652"/>
       <c r="I29" s="140"/>
       <c r="J29" s="140"/>
       <c r="K29" s="140"/>
@@ -26745,12 +26839,12 @@
     <row r="30" ht="21.9" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A30" s="354"/>
       <c r="B30" s="355"/>
-      <c r="C30" s="356"/>
-      <c r="D30" s="356"/>
-      <c r="E30" s="356"/>
-      <c r="F30" s="356"/>
-      <c r="G30" s="356"/>
-      <c r="H30" s="357"/>
+      <c r="C30" s="651"/>
+      <c r="D30" s="651"/>
+      <c r="E30" s="651"/>
+      <c r="F30" s="651"/>
+      <c r="G30" s="651"/>
+      <c r="H30" s="652"/>
       <c r="I30" s="140"/>
       <c r="J30" s="140"/>
       <c r="K30" s="140"/>
@@ -26772,12 +26866,12 @@
     <row r="31" ht="21.9" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A31" s="358"/>
       <c r="B31" s="359"/>
-      <c r="C31" s="360"/>
-      <c r="D31" s="360"/>
-      <c r="E31" s="360"/>
-      <c r="F31" s="360"/>
-      <c r="G31" s="360"/>
-      <c r="H31" s="361"/>
+      <c r="C31" s="653"/>
+      <c r="D31" s="653"/>
+      <c r="E31" s="653"/>
+      <c r="F31" s="653"/>
+      <c r="G31" s="653"/>
+      <c r="H31" s="654"/>
       <c r="I31" s="140"/>
       <c r="J31" s="140"/>
       <c r="K31" s="140"/>
@@ -27144,7 +27238,7 @@
       <c r="F43" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="G43" s="310" t="s">
+      <c r="G43" s="650" t="s">
         <v>25</v>
       </c>
       <c r="H43" s="140"/>
@@ -27326,24 +27420,14 @@
       <c r="Y48" s="140"/>
     </row>
     <row r="49" ht="21.9" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A49" s="324" t="s">
-        <v>96</v>
-      </c>
+      <c r="A49" s="324"/>
       <c r="B49" s="325"/>
-      <c r="C49" s="366" t="s">
-        <v>97</v>
-      </c>
-      <c r="D49" s="204" t="s">
-        <v>14</v>
-      </c>
+      <c r="C49" s="366"/>
+      <c r="D49" s="204"/>
       <c r="E49" s="204"/>
-      <c r="F49" s="367" t="s">
-        <v>98</v>
-      </c>
+      <c r="F49" s="367"/>
       <c r="G49" s="204"/>
-      <c r="H49" s="368" t="s">
-        <v>99</v>
-      </c>
+      <c r="H49" s="368"/>
       <c r="I49" s="140"/>
       <c r="J49" s="140"/>
       <c r="K49" s="140"/>
